--- a/outputs/Sorghum_flour_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_flour_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="83">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Yambio</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Minimal</t>
@@ -829,7 +832,7 @@
         <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J2" t="s">
         <v>74</v>
@@ -955,13 +958,13 @@
         <v>74</v>
       </c>
       <c r="AY2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1026,7 +1029,7 @@
         <v>74</v>
       </c>
       <c r="U3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V3" t="s">
         <v>74</v>
@@ -1038,7 +1041,7 @@
         <v>74</v>
       </c>
       <c r="Y3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z3" t="s">
         <v>74</v>
@@ -1116,13 +1119,13 @@
         <v>74</v>
       </c>
       <c r="AY3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1133,139 +1136,139 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
         <v>74</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N4" t="s">
         <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S4" t="s">
         <v>74</v>
       </c>
       <c r="T4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X4" t="s">
         <v>74</v>
       </c>
       <c r="Y4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="s">
         <v>74</v>
       </c>
       <c r="AH4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL4" t="s">
         <v>74</v>
       </c>
       <c r="AM4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="s">
         <v>74</v>
       </c>
       <c r="AP4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR4" t="s">
         <v>74</v>
       </c>
       <c r="AS4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT4" t="s">
         <v>74</v>
       </c>
       <c r="AU4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV4" t="s">
         <v>74</v>
@@ -1274,16 +1277,16 @@
         <v>74</v>
       </c>
       <c r="AX4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1342,37 +1345,37 @@
         <v>74</v>
       </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T5" t="s">
         <v>74</v>
       </c>
       <c r="U5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W5" t="s">
         <v>74</v>
       </c>
       <c r="X5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s">
         <v>74</v>
@@ -1408,10 +1411,10 @@
         <v>74</v>
       </c>
       <c r="AO5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ5" t="s">
         <v>74</v>
@@ -1420,13 +1423,13 @@
         <v>74</v>
       </c>
       <c r="AS5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV5" t="s">
         <v>74</v>
@@ -1435,16 +1438,16 @@
         <v>74</v>
       </c>
       <c r="AX5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1563,7 +1566,7 @@
         <v>74</v>
       </c>
       <c r="AM6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="s">
         <v>74</v>
@@ -1572,16 +1575,16 @@
         <v>74</v>
       </c>
       <c r="AP6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="s">
         <v>74</v>
@@ -1599,13 +1602,13 @@
         <v>74</v>
       </c>
       <c r="AY6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1664,22 +1667,22 @@
         <v>74</v>
       </c>
       <c r="S7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T7" t="s">
         <v>74</v>
       </c>
       <c r="U7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V7" t="s">
         <v>74</v>
       </c>
       <c r="W7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y7" t="s">
         <v>74</v>
@@ -1688,16 +1691,16 @@
         <v>74</v>
       </c>
       <c r="AA7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="s">
         <v>74</v>
       </c>
       <c r="AC7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE7" t="s">
         <v>74</v>
@@ -1706,22 +1709,22 @@
         <v>74</v>
       </c>
       <c r="AG7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="s">
         <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM7" t="s">
         <v>74</v>
@@ -1760,13 +1763,13 @@
         <v>74</v>
       </c>
       <c r="AY7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1849,10 +1852,10 @@
         <v>74</v>
       </c>
       <c r="AA8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC8" t="s">
         <v>74</v>
@@ -1921,13 +1924,13 @@
         <v>74</v>
       </c>
       <c r="AY8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2076,19 +2079,19 @@
         <v>74</v>
       </c>
       <c r="AW9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX9" t="s">
         <v>74</v>
       </c>
       <c r="AY9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2096,22 +2099,22 @@
         <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s">
         <v>74</v>
@@ -2201,55 +2204,55 @@
         <v>74</v>
       </c>
       <c r="AK10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="s">
         <v>74</v>
       </c>
       <c r="AO10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP10" t="s">
         <v>74</v>
       </c>
       <c r="AQ10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT10" t="s">
         <v>74</v>
       </c>
       <c r="AU10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2257,19 +2260,19 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
         <v>74</v>
@@ -2278,112 +2281,112 @@
         <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R11" t="s">
         <v>74</v>
       </c>
       <c r="S11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X11" t="s">
         <v>74</v>
       </c>
       <c r="Y11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="s">
         <v>74</v>
       </c>
       <c r="AA11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE11" t="s">
         <v>74</v>
       </c>
       <c r="AF11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s">
         <v>74</v>
       </c>
       <c r="AJ11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AO11" t="s">
         <v>74</v>
       </c>
       <c r="AP11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS11" t="s">
         <v>74</v>
@@ -2392,25 +2395,25 @@
         <v>74</v>
       </c>
       <c r="AU11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AV11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AW11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AZ11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BA11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2418,13 +2421,13 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>74</v>
@@ -2442,7 +2445,7 @@
         <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K12" t="s">
         <v>74</v>
@@ -2472,10 +2475,10 @@
         <v>74</v>
       </c>
       <c r="T12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V12" t="s">
         <v>74</v>
@@ -2523,13 +2526,13 @@
         <v>74</v>
       </c>
       <c r="AK12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s">
         <v>74</v>
       </c>
       <c r="AM12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="s">
         <v>74</v>
@@ -2541,10 +2544,10 @@
         <v>74</v>
       </c>
       <c r="AQ12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS12" t="s">
         <v>74</v>
@@ -2565,13 +2568,13 @@
         <v>74</v>
       </c>
       <c r="AY12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2618,7 +2621,7 @@
         <v>74</v>
       </c>
       <c r="O13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P13" t="s">
         <v>74</v>
@@ -2627,10 +2630,10 @@
         <v>74</v>
       </c>
       <c r="R13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T13" t="s">
         <v>74</v>
@@ -2651,13 +2654,13 @@
         <v>74</v>
       </c>
       <c r="Z13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC13" t="s">
         <v>74</v>
@@ -2669,22 +2672,22 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s">
         <v>74</v>
       </c>
       <c r="AK13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s">
         <v>74</v>
@@ -2699,10 +2702,10 @@
         <v>74</v>
       </c>
       <c r="AP13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR13" t="s">
         <v>74</v>
@@ -2711,7 +2714,7 @@
         <v>74</v>
       </c>
       <c r="AT13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU13" t="s">
         <v>74</v>
@@ -2726,13 +2729,13 @@
         <v>74</v>
       </c>
       <c r="AY13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2818,7 +2821,7 @@
         <v>74</v>
       </c>
       <c r="AB14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC14" t="s">
         <v>74</v>
@@ -2827,37 +2830,37 @@
         <v>74</v>
       </c>
       <c r="AE14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="s">
         <v>74</v>
       </c>
       <c r="AK14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AO14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP14" t="s">
         <v>74</v>
@@ -2866,7 +2869,7 @@
         <v>74</v>
       </c>
       <c r="AR14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS14" t="s">
         <v>74</v>
@@ -2875,25 +2878,25 @@
         <v>74</v>
       </c>
       <c r="AU14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV14" t="s">
         <v>74</v>
       </c>
       <c r="AW14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX14" t="s">
         <v>74</v>
       </c>
       <c r="AY14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2946,37 +2949,37 @@
         <v>74</v>
       </c>
       <c r="Q15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X15" t="s">
         <v>74</v>
       </c>
       <c r="Y15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="s">
         <v>74</v>
@@ -2988,7 +2991,7 @@
         <v>74</v>
       </c>
       <c r="AE15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF15" t="s">
         <v>74</v>
@@ -2997,13 +3000,13 @@
         <v>74</v>
       </c>
       <c r="AH15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s">
         <v>74</v>
       </c>
       <c r="AJ15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK15" t="s">
         <v>74</v>
@@ -3012,7 +3015,7 @@
         <v>74</v>
       </c>
       <c r="AM15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="s">
         <v>74</v>
@@ -3021,10 +3024,10 @@
         <v>74</v>
       </c>
       <c r="AP15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR15" t="s">
         <v>74</v>
@@ -3048,13 +3051,13 @@
         <v>74</v>
       </c>
       <c r="AY15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3065,10 +3068,10 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
         <v>74</v>
@@ -3077,7 +3080,7 @@
         <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s">
         <v>74</v>
@@ -3134,7 +3137,7 @@
         <v>74</v>
       </c>
       <c r="Z16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA16" t="s">
         <v>74</v>
@@ -3149,25 +3152,25 @@
         <v>74</v>
       </c>
       <c r="AE16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG16" t="s">
         <v>74</v>
       </c>
       <c r="AH16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s">
         <v>74</v>
       </c>
       <c r="AK16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="s">
         <v>74</v>
@@ -3194,28 +3197,28 @@
         <v>74</v>
       </c>
       <c r="AT16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX16" t="s">
         <v>74</v>
       </c>
       <c r="AY16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3247,10 +3250,10 @@
         <v>74</v>
       </c>
       <c r="J17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L17" t="s">
         <v>74</v>
@@ -3268,7 +3271,7 @@
         <v>74</v>
       </c>
       <c r="Q17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R17" t="s">
         <v>74</v>
@@ -3343,40 +3346,40 @@
         <v>74</v>
       </c>
       <c r="AP17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW17" t="s">
         <v>74</v>
       </c>
       <c r="AX17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3384,19 +3387,19 @@
         <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
         <v>74</v>
@@ -3405,7 +3408,7 @@
         <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J18" t="s">
         <v>74</v>
@@ -3414,25 +3417,25 @@
         <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S18" t="s">
         <v>74</v>
@@ -3441,10 +3444,10 @@
         <v>74</v>
       </c>
       <c r="U18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W18" t="s">
         <v>74</v>
@@ -3453,13 +3456,13 @@
         <v>74</v>
       </c>
       <c r="Y18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z18" t="s">
         <v>74</v>
       </c>
       <c r="AA18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB18" t="s">
         <v>74</v>
@@ -3468,58 +3471,58 @@
         <v>74</v>
       </c>
       <c r="AD18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG18" t="s">
         <v>74</v>
       </c>
       <c r="AH18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="s">
         <v>74</v>
       </c>
       <c r="AK18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="s">
         <v>74</v>
       </c>
       <c r="AM18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AO18" t="s">
         <v>74</v>
       </c>
       <c r="AP18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ18" t="s">
         <v>74</v>
       </c>
       <c r="AR18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV18" t="s">
         <v>74</v>
@@ -3528,16 +3531,16 @@
         <v>74</v>
       </c>
       <c r="AX18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AZ18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BA18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3545,22 +3548,22 @@
         <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
         <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
         <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>74</v>
@@ -3569,16 +3572,16 @@
         <v>74</v>
       </c>
       <c r="J19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N19" t="s">
         <v>74</v>
@@ -3587,7 +3590,7 @@
         <v>74</v>
       </c>
       <c r="P19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q19" t="s">
         <v>74</v>
@@ -3596,94 +3599,94 @@
         <v>74</v>
       </c>
       <c r="S19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AA19" t="s">
         <v>74</v>
       </c>
       <c r="AB19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG19" t="s">
         <v>74</v>
       </c>
       <c r="AH19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ19" t="s">
         <v>74</v>
       </c>
       <c r="AK19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="s">
         <v>74</v>
       </c>
       <c r="AM19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AO19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AP19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ19" t="s">
         <v>74</v>
       </c>
       <c r="AR19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW19" t="s">
         <v>74</v>
@@ -3692,13 +3695,13 @@
         <v>74</v>
       </c>
       <c r="AY19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3811,7 +3814,7 @@
         <v>74</v>
       </c>
       <c r="AK20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s">
         <v>74</v>
@@ -3838,7 +3841,7 @@
         <v>74</v>
       </c>
       <c r="AT20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU20" t="s">
         <v>74</v>
@@ -3853,13 +3856,13 @@
         <v>74</v>
       </c>
       <c r="AY20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3867,136 +3870,136 @@
         <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
         <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s">
         <v>74</v>
       </c>
       <c r="L21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O21" t="s">
         <v>74</v>
       </c>
       <c r="P21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R21" t="s">
         <v>74</v>
       </c>
       <c r="S21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W21" t="s">
         <v>74</v>
       </c>
       <c r="X21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z21" t="s">
         <v>74</v>
       </c>
       <c r="AA21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AB21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC21" t="s">
         <v>74</v>
       </c>
       <c r="AD21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AF21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s">
         <v>74</v>
       </c>
       <c r="AJ21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="s">
         <v>74</v>
       </c>
       <c r="AM21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>74</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ21" t="s">
         <v>76</v>
       </c>
-      <c r="AO21" t="s">
-        <v>74</v>
-      </c>
-      <c r="AP21" t="s">
-        <v>76</v>
-      </c>
-      <c r="AQ21" t="s">
-        <v>75</v>
-      </c>
       <c r="AR21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT21" t="s">
         <v>74</v>
@@ -4005,22 +4008,22 @@
         <v>74</v>
       </c>
       <c r="AV21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AW21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AY21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AZ21" t="s">
         <v>79</v>
       </c>
-      <c r="AZ21" t="s">
-        <v>78</v>
-      </c>
       <c r="BA21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4031,19 +4034,19 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
         <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s">
         <v>74</v>
@@ -4148,22 +4151,22 @@
         <v>74</v>
       </c>
       <c r="AP22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AQ22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AR22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AS22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AT22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AU22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AV22" t="s">
         <v>74</v>
@@ -4172,16 +4175,16 @@
         <v>74</v>
       </c>
       <c r="AX22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AY22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AZ22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="BA22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_flour_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_flour_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="77">
   <si>
     <t>2020 Mar</t>
   </si>
@@ -244,25 +244,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>8%</t>
   </si>
 </sst>
 </file>
@@ -832,7 +814,7 @@
         <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
         <v>74</v>
@@ -958,13 +940,13 @@
         <v>74</v>
       </c>
       <c r="AY2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -1029,7 +1011,7 @@
         <v>74</v>
       </c>
       <c r="U3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V3" t="s">
         <v>74</v>
@@ -1041,7 +1023,7 @@
         <v>74</v>
       </c>
       <c r="Y3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z3" t="s">
         <v>74</v>
@@ -1119,13 +1101,13 @@
         <v>74</v>
       </c>
       <c r="AY3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -1280,13 +1262,13 @@
         <v>75</v>
       </c>
       <c r="AY4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -1345,7 +1327,7 @@
         <v>74</v>
       </c>
       <c r="S5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T5" t="s">
         <v>74</v>
@@ -1360,19 +1342,19 @@
         <v>74</v>
       </c>
       <c r="X5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z5" t="s">
         <v>75</v>
       </c>
       <c r="AA5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AB5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s">
         <v>75</v>
@@ -1414,7 +1396,7 @@
         <v>75</v>
       </c>
       <c r="AP5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ5" t="s">
         <v>74</v>
@@ -1429,7 +1411,7 @@
         <v>75</v>
       </c>
       <c r="AU5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AV5" t="s">
         <v>74</v>
@@ -1441,13 +1423,13 @@
         <v>75</v>
       </c>
       <c r="AY5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -1566,7 +1548,7 @@
         <v>74</v>
       </c>
       <c r="AM6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AN6" t="s">
         <v>74</v>
@@ -1575,16 +1557,16 @@
         <v>74</v>
       </c>
       <c r="AP6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AR6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT6" t="s">
         <v>74</v>
@@ -1602,13 +1584,13 @@
         <v>74</v>
       </c>
       <c r="AY6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -1667,7 +1649,7 @@
         <v>74</v>
       </c>
       <c r="S7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T7" t="s">
         <v>74</v>
@@ -1682,7 +1664,7 @@
         <v>75</v>
       </c>
       <c r="X7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Y7" t="s">
         <v>74</v>
@@ -1691,16 +1673,16 @@
         <v>74</v>
       </c>
       <c r="AA7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AB7" t="s">
         <v>74</v>
       </c>
       <c r="AC7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AD7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AE7" t="s">
         <v>74</v>
@@ -1712,7 +1694,7 @@
         <v>75</v>
       </c>
       <c r="AH7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI7" t="s">
         <v>75</v>
@@ -1721,10 +1703,10 @@
         <v>74</v>
       </c>
       <c r="AK7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AM7" t="s">
         <v>74</v>
@@ -1763,13 +1745,13 @@
         <v>74</v>
       </c>
       <c r="AY7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -1852,10 +1834,10 @@
         <v>74</v>
       </c>
       <c r="AA8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AB8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC8" t="s">
         <v>74</v>
@@ -1924,13 +1906,13 @@
         <v>74</v>
       </c>
       <c r="AY8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -2079,19 +2061,19 @@
         <v>74</v>
       </c>
       <c r="AW9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AX9" t="s">
         <v>74</v>
       </c>
       <c r="AY9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -2105,13 +2087,13 @@
         <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
         <v>75</v>
@@ -2225,19 +2207,19 @@
         <v>75</v>
       </c>
       <c r="AR10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT10" t="s">
         <v>74</v>
       </c>
       <c r="AU10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AV10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AW10" t="s">
         <v>75</v>
@@ -2246,13 +2228,13 @@
         <v>75</v>
       </c>
       <c r="AY10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -2395,10 +2377,10 @@
         <v>74</v>
       </c>
       <c r="AU11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AV11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AW11" t="s">
         <v>75</v>
@@ -2407,13 +2389,13 @@
         <v>75</v>
       </c>
       <c r="AY11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AZ11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="BA11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:53">
@@ -2421,13 +2403,13 @@
         <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>74</v>
@@ -2445,7 +2427,7 @@
         <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s">
         <v>74</v>
@@ -2478,7 +2460,7 @@
         <v>75</v>
       </c>
       <c r="U12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V12" t="s">
         <v>74</v>
@@ -2526,13 +2508,13 @@
         <v>74</v>
       </c>
       <c r="AK12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL12" t="s">
         <v>74</v>
       </c>
       <c r="AM12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AN12" t="s">
         <v>74</v>
@@ -2544,7 +2526,7 @@
         <v>74</v>
       </c>
       <c r="AQ12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AR12" t="s">
         <v>75</v>
@@ -2568,13 +2550,13 @@
         <v>74</v>
       </c>
       <c r="AY12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:53">
@@ -2654,13 +2636,13 @@
         <v>74</v>
       </c>
       <c r="Z13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA13" t="s">
         <v>75</v>
       </c>
       <c r="AB13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s">
         <v>74</v>
@@ -2672,22 +2654,22 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="s">
         <v>75</v>
       </c>
       <c r="AI13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s">
         <v>74</v>
       </c>
       <c r="AK13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL13" t="s">
         <v>74</v>
@@ -2729,13 +2711,13 @@
         <v>74</v>
       </c>
       <c r="AY13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:53">
@@ -2830,16 +2812,16 @@
         <v>74</v>
       </c>
       <c r="AE14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AF14" t="s">
         <v>75</v>
       </c>
       <c r="AG14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AH14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AI14" t="s">
         <v>75</v>
@@ -2851,16 +2833,16 @@
         <v>75</v>
       </c>
       <c r="AL14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AM14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AN14" t="s">
         <v>75</v>
       </c>
       <c r="AO14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AP14" t="s">
         <v>74</v>
@@ -2890,13 +2872,13 @@
         <v>74</v>
       </c>
       <c r="AY14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:53">
@@ -2949,7 +2931,7 @@
         <v>74</v>
       </c>
       <c r="Q15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R15" t="s">
         <v>75</v>
@@ -2958,25 +2940,25 @@
         <v>75</v>
       </c>
       <c r="T15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="V15" t="s">
         <v>75</v>
       </c>
       <c r="W15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="X15" t="s">
         <v>74</v>
       </c>
       <c r="Y15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA15" t="s">
         <v>75</v>
@@ -3006,7 +2988,7 @@
         <v>74</v>
       </c>
       <c r="AJ15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AK15" t="s">
         <v>74</v>
@@ -3051,13 +3033,13 @@
         <v>74</v>
       </c>
       <c r="AY15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:53">
@@ -3068,10 +3050,10 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>74</v>
@@ -3137,7 +3119,7 @@
         <v>74</v>
       </c>
       <c r="Z16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AA16" t="s">
         <v>74</v>
@@ -3155,7 +3137,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AG16" t="s">
         <v>74</v>
@@ -3203,7 +3185,7 @@
         <v>75</v>
       </c>
       <c r="AV16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AW16" t="s">
         <v>75</v>
@@ -3212,13 +3194,13 @@
         <v>74</v>
       </c>
       <c r="AY16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -3271,7 +3253,7 @@
         <v>74</v>
       </c>
       <c r="Q17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R17" t="s">
         <v>74</v>
@@ -3346,16 +3328,16 @@
         <v>74</v>
       </c>
       <c r="AP17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AR17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT17" t="s">
         <v>75</v>
@@ -3364,22 +3346,22 @@
         <v>75</v>
       </c>
       <c r="AV17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AW17" t="s">
         <v>74</v>
       </c>
       <c r="AX17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AY17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:53">
@@ -3417,7 +3399,7 @@
         <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M18" t="s">
         <v>75</v>
@@ -3432,7 +3414,7 @@
         <v>75</v>
       </c>
       <c r="Q18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R18" t="s">
         <v>75</v>
@@ -3474,7 +3456,7 @@
         <v>75</v>
       </c>
       <c r="AE18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AF18" t="s">
         <v>75</v>
@@ -3498,7 +3480,7 @@
         <v>74</v>
       </c>
       <c r="AM18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AN18" t="s">
         <v>75</v>
@@ -3531,16 +3513,16 @@
         <v>74</v>
       </c>
       <c r="AX18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AY18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AZ18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="BA18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:53">
@@ -3695,13 +3677,13 @@
         <v>74</v>
       </c>
       <c r="AY19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:53">
@@ -3814,7 +3796,7 @@
         <v>74</v>
       </c>
       <c r="AK20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AL20" t="s">
         <v>74</v>
@@ -3841,7 +3823,7 @@
         <v>74</v>
       </c>
       <c r="AT20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AU20" t="s">
         <v>74</v>
@@ -3856,13 +3838,13 @@
         <v>74</v>
       </c>
       <c r="AY20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:53">
@@ -3984,16 +3966,16 @@
         <v>75</v>
       </c>
       <c r="AN21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AO21" t="s">
         <v>74</v>
       </c>
       <c r="AP21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AQ21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AR21" t="s">
         <v>75</v>
@@ -4014,16 +3996,16 @@
         <v>75</v>
       </c>
       <c r="AX21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AY21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AZ21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="BA21" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:53">
@@ -4034,13 +4016,13 @@
         <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
         <v>74</v>
@@ -4151,22 +4133,22 @@
         <v>74</v>
       </c>
       <c r="AP22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AQ22" t="s">
         <v>75</v>
       </c>
       <c r="AR22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AS22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AT22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AU22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AV22" t="s">
         <v>74</v>
@@ -4175,16 +4157,16 @@
         <v>74</v>
       </c>
       <c r="AX22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AY22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AZ22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="BA22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Sorghum_flour_tukey_classification_matrix.xlsx
+++ b/outputs/Sorghum_flour_tukey_classification_matrix.xlsx
@@ -241,7 +241,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
